--- a/results/Int Remove ACC.xlsx
+++ b/results/Int Remove ACC.xlsx
@@ -878,52 +878,52 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>67.37 ± 5.34</t>
+          <t>67.65 ± 5.97</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>67.99 ± 4.96</t>
+          <t>68.25 ± 5.64</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>67.36 ± 5.42</t>
+          <t>67.60 ± 6.10</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>74.10 ± 5.88</t>
+          <t>74.11 ± 5.86</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>77.35 ± 6.54</t>
+          <t>77.62 ± 6.31</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>34.93 ± 10.47</t>
+          <t>35.48 ± 11.78</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>77.31 ± 6.56</t>
+          <t>77.58 ± 6.34</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>31.48 ± 4.80</t>
+          <t>31.26 ± 5.58</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>39.97 ± 15.23</t>
+          <t>40.44 ± 13.60</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>29.44 ± 15.80</t>
+          <t>29.26 ± 14.17</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -1310,52 +1310,52 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>67.62 ± 5.39</t>
+          <t>67.64 ± 6.30</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>68.18 ± 4.97</t>
+          <t>68.25 ± 5.94</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>67.57 ± 5.45</t>
+          <t>67.61 ± 6.42</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>74.24 ± 5.71</t>
+          <t>73.79 ± 6.57</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>77.51 ± 6.29</t>
+          <t>77.35 ± 6.90</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>35.39 ± 10.59</t>
+          <t>35.47 ± 12.44</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>77.47 ± 6.29</t>
+          <t>77.33 ± 6.91</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>31.31 ± 4.88</t>
+          <t>31.66 ± 6.17</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>41.38 ± 14.49</t>
+          <t>40.63 ± 16.24</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>30.91 ± 14.94</t>
+          <t>29.60 ± 15.22</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -1742,52 +1742,52 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>67.18 ± 5.86</t>
+          <t>67.74 ± 5.73</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>67.85 ± 5.53</t>
+          <t>68.37 ± 5.41</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>67.20 ± 5.95</t>
+          <t>67.72 ± 5.87</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>73.97 ± 6.07</t>
+          <t>74.19 ± 6.45</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>77.19 ± 6.56</t>
+          <t>77.42 ± 6.78</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>34.59 ± 11.52</t>
+          <t>35.69 ± 11.30</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>77.16 ± 6.57</t>
+          <t>77.40 ± 6.79</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>31.76 ± 4.95</t>
+          <t>31.59 ± 5.87</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>39.70 ± 14.98</t>
+          <t>40.77 ± 14.47</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>29.77 ± 15.31</t>
+          <t>29.82 ± 15.00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -2174,52 +2174,52 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>67.68 ± 5.67</t>
+          <t>68.14 ± 6.29</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>68.24 ± 5.29</t>
+          <t>68.70 ± 5.96</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>67.66 ± 5.71</t>
+          <t>68.11 ± 6.37</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>74.14 ± 5.87</t>
+          <t>74.28 ± 6.47</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>77.92 ± 5.98</t>
+          <t>77.64 ± 6.58</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>35.51 ± 11.12</t>
+          <t>36.44 ± 12.38</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>77.90 ± 5.98</t>
+          <t>77.60 ± 6.60</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>31.17 ± 5.21</t>
+          <t>30.82 ± 5.92</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>40.42 ± 14.55</t>
+          <t>41.15 ± 15.51</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>30.28 ± 14.84</t>
+          <t>30.35 ± 14.63</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -2606,52 +2606,52 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>67.76 ± 5.30</t>
+          <t>67.53 ± 6.14</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>68.38 ± 4.90</t>
+          <t>68.20 ± 5.68</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>67.74 ± 5.41</t>
+          <t>67.47 ± 6.23</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>74.18 ± 5.74</t>
+          <t>74.14 ± 5.97</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>77.93 ± 6.41</t>
+          <t>77.83 ± 5.93</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>35.72 ± 10.42</t>
+          <t>35.27 ± 12.07</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>77.92 ± 6.42</t>
+          <t>77.81 ± 5.94</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>31.68 ± 4.95</t>
+          <t>31.32 ± 5.34</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>41.12 ± 14.61</t>
+          <t>41.91 ± 14.72</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>30.73 ± 14.82</t>
+          <t>30.93 ± 14.76</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -3038,52 +3038,52 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>68.09 ± 4.29</t>
+          <t>68.91 ± 3.10</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>68.60 ± 4.28</t>
+          <t>69.44 ± 2.97</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>68.14 ± 4.44</t>
+          <t>68.96 ± 3.19</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>75.81 ± 4.09</t>
+          <t>76.46 ± 3.56</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>78.76 ± 5.87</t>
+          <t>79.71 ± 5.02</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>36.42 ± 8.49</t>
+          <t>38.08 ± 6.01</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>78.75 ± 5.88</t>
+          <t>79.70 ± 5.02</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>30.82 ± 4.35</t>
+          <t>29.72 ± 2.85</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>41.45 ± 10.87</t>
+          <t>42.84 ± 10.31</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>32.13 ± 11.09</t>
+          <t>33.43 ± 11.38</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -3470,52 +3470,52 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>70.51 ± 4.87</t>
+          <t>71.15 ± 5.62</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>71.04 ± 4.89</t>
+          <t>71.68 ± 5.50</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>70.70 ± 4.94</t>
+          <t>71.36 ± 5.62</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>77.76 ± 5.85</t>
+          <t>78.34 ± 6.20</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>79.72 ± 5.92</t>
+          <t>80.36 ± 6.07</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>41.35 ± 9.76</t>
+          <t>42.60 ± 11.21</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>79.69 ± 5.94</t>
+          <t>80.34 ± 6.08</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>28.68 ± 5.16</t>
+          <t>27.69 ± 5.82</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>43.43 ± 10.86</t>
+          <t>46.67 ± 11.29</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>32.20 ± 11.38</t>
+          <t>33.54 ± 11.68</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -3902,52 +3902,52 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>69.02 ± 5.75</t>
+          <t>70.04 ± 6.43</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>69.18 ± 5.69</t>
+          <t>70.18 ± 6.34</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>68.96 ± 5.84</t>
+          <t>69.94 ± 6.59</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>74.90 ± 7.99</t>
+          <t>75.57 ± 8.18</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>76.70 ± 8.41</t>
+          <t>76.89 ± 9.33</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>38.09 ± 11.51</t>
+          <t>40.11 ± 12.86</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>76.72 ± 8.43</t>
+          <t>76.86 ± 9.35</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>30.39 ± 6.11</t>
+          <t>30.19 ± 6.62</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>42.88 ± 16.22</t>
+          <t>44.42 ± 18.77</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>32.28 ± 15.92</t>
+          <t>33.75 ± 17.47</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -4334,52 +4334,52 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>68.73 ± 6.34</t>
+          <t>68.83 ± 5.99</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>68.66 ± 6.25</t>
+          <t>68.77 ± 5.91</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>68.45 ± 6.58</t>
+          <t>68.58 ± 6.18</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>74.80 ± 6.98</t>
+          <t>74.84 ± 7.40</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>77.19 ± 6.78</t>
+          <t>77.13 ± 7.20</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>37.36 ± 12.54</t>
+          <t>37.56 ± 11.88</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>77.17 ± 6.79</t>
+          <t>77.12 ± 7.21</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>31.33 ± 6.07</t>
+          <t>32.01 ± 6.61</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>45.63 ± 11.86</t>
+          <t>45.00 ± 12.38</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>34.43 ± 13.53</t>
+          <t>36.15 ± 14.55</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -4766,52 +4766,52 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>69.45 ± 7.15</t>
+          <t>69.15 ± 7.71</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>69.74 ± 6.85</t>
+          <t>69.48 ± 7.44</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>69.02 ± 8.01</t>
+          <t>68.81 ± 8.41</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>76.16 ± 7.03</t>
+          <t>76.21 ± 7.16</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>75.28 ± 8.28</t>
+          <t>75.64 ± 8.28</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>38.94 ± 14.15</t>
+          <t>38.36 ± 15.26</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>75.26 ± 8.30</t>
+          <t>75.63 ± 8.29</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>29.87 ± 5.59</t>
+          <t>30.12 ± 6.19</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>41.38 ± 14.02</t>
+          <t>41.95 ± 15.56</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>29.99 ± 14.17</t>
+          <t>31.17 ± 13.48</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
@@ -5198,52 +5198,52 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>71.27 ± 9.48</t>
+          <t>70.94 ± 9.01</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>71.10 ± 9.51</t>
+          <t>70.75 ± 8.98</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>70.59 ± 10.38</t>
+          <t>70.27 ± 9.81</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>76.59 ± 10.92</t>
+          <t>76.26 ± 11.32</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>75.83 ± 11.42</t>
+          <t>75.99 ± 11.51</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>42.29 ± 18.81</t>
+          <t>41.60 ± 17.84</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>75.80 ± 11.46</t>
+          <t>75.97 ± 11.54</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>29.94 ± 9.52</t>
+          <t>29.32 ± 9.45</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>45.67 ± 17.00</t>
+          <t>46.48 ± 17.59</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>32.95 ± 17.26</t>
+          <t>32.82 ± 17.34</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -5630,52 +5630,52 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>69.00 ± 5.67</t>
+          <t>68.46 ± 5.76</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>69.67 ± 5.96</t>
+          <t>69.18 ± 6.46</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>69.22 ± 5.89</t>
+          <t>68.71 ± 6.34</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>78.40 ± 8.42</t>
+          <t>77.93 ± 8.03</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>70.20 ± 12.07</t>
+          <t>70.07 ± 11.50</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>37.89 ± 11.20</t>
+          <t>36.93 ± 11.70</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>70.16 ± 12.10</t>
+          <t>70.03 ± 11.53</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>29.80 ± 7.08</t>
+          <t>29.71 ± 6.72</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>41.74 ± 20.32</t>
+          <t>40.08 ± 20.73</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>30.02 ± 20.98</t>
+          <t>29.64 ± 19.92</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -6062,52 +6062,52 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>70.08 ± 8.62</t>
+          <t>69.51 ± 7.37</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>71.50 ± 7.88</t>
+          <t>71.06 ± 6.54</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>71.20 ± 7.89</t>
+          <t>70.70 ± 6.60</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>79.47 ± 8.37</t>
+          <t>79.46 ± 7.77</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>70.38 ± 12.26</t>
+          <t>69.55 ± 12.11</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>39.74 ± 16.60</t>
+          <t>38.65 ± 14.06</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>70.33 ± 12.29</t>
+          <t>69.49 ± 12.14</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>27.47 ± 7.88</t>
+          <t>27.36 ± 7.22</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>46.08 ± 17.64</t>
+          <t>43.21 ± 18.45</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>32.63 ± 18.05</t>
+          <t>31.74 ± 18.55</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -6494,52 +6494,52 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>68.88 ± 9.80</t>
+          <t>69.34 ± 10.21</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>71.33 ± 8.38</t>
+          <t>71.70 ± 8.80</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>70.81 ± 8.79</t>
+          <t>71.17 ± 9.29</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>78.65 ± 11.19</t>
+          <t>78.29 ± 11.28</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>68.72 ± 13.31</t>
+          <t>68.25 ± 13.12</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>37.56 ± 18.97</t>
+          <t>38.42 ± 19.80</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>68.68 ± 13.33</t>
+          <t>68.20 ± 13.14</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>27.99 ± 10.02</t>
+          <t>27.86 ± 10.16</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>45.75 ± 19.84</t>
+          <t>46.24 ± 19.31</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>30.33 ± 14.94</t>
+          <t>29.42 ± 14.53</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -6926,52 +6926,52 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>68.01 ± 11.36</t>
+          <t>67.49 ± 11.60</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>73.43 ± 7.83</t>
+          <t>72.58 ± 7.65</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>72.25 ± 8.80</t>
+          <t>71.40 ± 8.94</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>78.00 ± 11.05</t>
+          <t>77.37 ± 11.15</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>62.28 ± 16.17</t>
+          <t>61.10 ± 15.39</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>35.56 ± 20.42</t>
+          <t>33.92 ± 20.69</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>62.18 ± 16.22</t>
+          <t>61.01 ± 15.43</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>28.75 ± 10.02</t>
+          <t>29.09 ± 10.12</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>44.70 ± 23.16</t>
+          <t>41.59 ± 23.21</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>32.77 ± 22.17</t>
+          <t>31.03 ± 18.40</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -7358,52 +7358,52 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>64.79 ± 9.91</t>
+          <t>65.17 ± 9.64</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>74.37 ± 6.66</t>
+          <t>74.98 ± 6.59</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>73.00 ± 7.51</t>
+          <t>73.50 ± 7.57</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>75.37 ± 9.22</t>
+          <t>77.04 ± 8.89</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>52.20 ± 15.05</t>
+          <t>54.91 ± 14.76</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>30.07 ± 18.99</t>
+          <t>31.19 ± 18.98</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>52.08 ± 15.09</t>
+          <t>54.83 ± 14.80</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>32.48 ± 8.65</t>
+          <t>30.89 ± 8.36</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>34.75 ± 19.55</t>
+          <t>36.59 ± 19.16</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>25.34 ± 21.96</t>
+          <t>26.42 ± 22.01</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -7790,52 +7790,52 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>59.56 ± 11.90</t>
+          <t>60.37 ± 13.19</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>75.38 ± 8.03</t>
+          <t>76.24 ± 7.70</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>72.99 ± 9.19</t>
+          <t>73.38 ± 9.56</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>74.51 ± 14.35</t>
+          <t>73.96 ± 15.12</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>45.26 ± 21.91</t>
+          <t>45.33 ± 22.99</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>19.92 ± 24.84</t>
+          <t>20.92 ± 26.72</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>45.16 ± 21.94</t>
+          <t>45.24 ± 23.02</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>31.62 ± 14.28</t>
+          <t>30.85 ± 14.15</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>35.26 ± 29.57</t>
+          <t>34.06 ± 31.07</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>22.22 ± 30.66</t>
+          <t>21.60 ± 32.60</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
@@ -8222,52 +8222,52 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>61.50 ± 7.46</t>
+          <t>63.52 ± 9.27</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>81.97 ± 4.65</t>
+          <t>82.53 ± 5.70</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>79.46 ± 4.84</t>
+          <t>80.18 ± 6.48</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>81.83 ± 9.71</t>
+          <t>81.66 ± 10.57</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>53.55 ± 19.78</t>
+          <t>55.40 ± 22.78</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>26.82 ± 16.32</t>
+          <t>30.75 ± 21.24</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>53.21 ± 19.87</t>
+          <t>55.28 ± 22.83</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>24.65 ± 9.54</t>
+          <t>25.17 ± 10.07</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>47.38 ± 29.85</t>
+          <t>48.40 ± 28.72</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>38.70 ± 26.63</t>
+          <t>40.04 ± 26.86</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -8654,52 +8654,52 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>61.10 ± 9.58</t>
+          <t>61.06 ± 9.81</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>83.17 ± 4.93</t>
+          <t>83.24 ± 4.94</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>80.66 ± 5.43</t>
+          <t>80.62 ± 5.57</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>84.67 ± 11.87</t>
+          <t>85.22 ± 10.67</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>57.54 ± 24.90</t>
+          <t>57.79 ± 23.85</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>26.55 ± 20.74</t>
+          <t>26.49 ± 21.28</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>57.41 ± 24.93</t>
+          <t>57.65 ± 23.88</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>22.46 ± 11.70</t>
+          <t>22.02 ± 11.19</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>58.27 ± 30.31</t>
+          <t>58.92 ± 31.16</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>48.70 ± 31.21</t>
+          <t>47.12 ± 30.55</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -9086,52 +9086,52 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>55.42 ± 8.71</t>
+          <t>54.09 ± 8.27</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>82.28 ± 5.51</t>
+          <t>81.37 ± 5.95</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>79.60 ± 5.55</t>
+          <t>78.73 ± 5.88</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>74.06 ± 18.94</t>
+          <t>74.48 ± 18.38</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>42.10 ± 28.32</t>
+          <t>42.23 ± 29.49</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>14.57 ± 21.84</t>
+          <t>11.57 ± 20.92</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>41.97 ± 28.34</t>
+          <t>42.12 ± 29.52</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>30.91 ± 17.75</t>
+          <t>28.78 ± 16.51</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>38.59 ± 35.41</t>
+          <t>38.80 ± 39.14</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>28.01 ± 35.24</t>
+          <t>28.32 ± 36.87</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -9518,52 +9518,52 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>57.73 ± 14.26</t>
+          <t>56.46 ± 15.04</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>82.69 ± 7.17</t>
+          <t>82.74 ± 7.43</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>80.53 ± 7.48</t>
+          <t>80.09 ± 7.70</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>72.87 ± 17.00</t>
+          <t>73.88 ± 16.74</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>33.21 ± 22.43</t>
+          <t>34.56 ± 23.25</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>8.61 ± 15.68</t>
+          <t>5.62 ± 16.39</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>38.09 ± 19.93</t>
+          <t>39.43 ± 20.53</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>38.88 ± 24.69</t>
+          <t>37.36 ± 24.04</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>30.19 ± 29.94</t>
+          <t>32.53 ± 29.12</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>18.24 ± 20.35</t>
+          <t>21.14 ± 22.51</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
